--- a/public/templates/mantolama-teklif-sablonu.xlsx
+++ b/public/templates/mantolama-teklif-sablonu.xlsx
@@ -22,7 +22,7 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="61">
   <si>
-    <t xml:space="preserve">ÖZERGRUP YALITIM VE İZOLASYON A.Ş.</t>
+    <t xml:space="preserve">ÖZER GRUP YALITIM İZOLASYON A.Ş.</t>
   </si>
   <si>
     <t xml:space="preserve">Mescit Mah. Ulugüney Sk. Harman Plaza A1 Blok K2 No:15 Tuzla / İstanbul</t>
@@ -160,7 +160,7 @@
     <t>VAKIFBANK</t>
   </si>
   <si>
-    <t xml:space="preserve">TR54 0001 5001 5800 7223 2324 14</t>
+    <t xml:space="preserve">TR54 0001 5001 5800 7323 2324 14</t>
   </si>
   <si>
     <t>Nakliye</t>
